--- a/Data/EXCEL/Transfer/salemon/20240711/6829-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6829-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0FED1BC-71BD-45BD-B618-A20C00C13952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BB74B5E-1AE2-4B87-A176-1B899411CA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{A7FC3E95-4478-432F-8B6E-2AAF05122A0C}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{99D02D88-670E-431A-9016-EE93759B97D2}"/>
   </bookViews>
   <sheets>
     <sheet name="6829-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,21 +1261,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3743BB67-B201-4006-88E9-12803091F2D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947B418A-93C1-4ED4-8302-6624789ED097}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1302,7 +1302,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1384,7 +1384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1423,7 +1423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>61.2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>-24.3</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>-24.7</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>-28.2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>-28.5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>-30.2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>-32</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>-33.799999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>-37</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>-39.1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>-38.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>-45.2</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>-51.4</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>42.1</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>76.099999999999994</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>381.4</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>502.5</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>1005.2</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3543,217 +3543,217 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="10">
         <v>44256</v>
       </c>
